--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488094_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488094_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6341</v>
+        <v>9.0444</v>
       </c>
       <c r="E2" t="n">
         <v>5.5255</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1086</v>
+        <v>3.5189</v>
       </c>
       <c r="G2" t="n">
         <v>3.1337</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4143</v>
+        <v>-0.1754</v>
       </c>
       <c r="T2" t="n">
         <v>-0.2568</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6711</v>
+        <v>0.0814</v>
       </c>
       <c r="V2" t="n">
         <v>5.095</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7505</v>
+        <v>7.9295</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1851</v>
+        <v>6.0832</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5655</v>
+        <v>1.8463</v>
       </c>
       <c r="G3" t="n">
         <v>4.5384</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7195</v>
+        <v>-0.5405</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1944</v>
+        <v>-0.2963</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.525</v>
+        <v>-0.2442</v>
       </c>
       <c r="V3" t="n">
         <v>2.1476</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4372</v>
+        <v>4.9547</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4543</v>
+        <v>3.4772</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9829</v>
+        <v>1.4774</v>
       </c>
       <c r="G4" t="n">
         <v>4.2478</v>
@@ -766,13 +766,13 @@
         <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.577</v>
+        <v>0.0945</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3816</v>
+        <v>-0.3587</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9586</v>
+        <v>0.4532</v>
       </c>
       <c r="V4" t="n">
         <v>1.2071</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2968</v>
+        <v>4.3374</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9893</v>
+        <v>4.1141</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3075</v>
+        <v>0.2233</v>
       </c>
       <c r="G5" t="n">
         <v>4.7775</v>
@@ -844,13 +844,13 @@
         <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4123</v>
+        <v>-0.3717</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.444</v>
+        <v>-0.3192</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0318</v>
+        <v>-0.0525</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2666</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>A. FIDALGO PEDUZZI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.508</v>
+        <v>1.6166</v>
       </c>
       <c r="E6" t="n">
-        <v>1.508</v>
+        <v>0.3726</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.244</v>
       </c>
       <c r="G6" t="n">
-        <v>1.508</v>
+        <v>3.3681</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3027</v>
+        <v>1.2923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2053</v>
+        <v>2.0758</v>
       </c>
       <c r="J6" t="n">
-        <v>1.508</v>
+        <v>2.7356</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3027</v>
+        <v>0.8071</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2053</v>
+        <v>1.9285</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.6324</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.4852</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.1472</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.4937</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.3808</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.113</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FIDALGO PEDUZZI</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1145</v>
+        <v>1.508</v>
       </c>
       <c r="E7" t="n">
-        <v>0.067</v>
+        <v>1.508</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0474</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3681</v>
+        <v>1.508</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2923</v>
+        <v>0.3027</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0758</v>
+        <v>1.2053</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7356</v>
+        <v>1.508</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8071</v>
+        <v>0.3027</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9285</v>
+        <v>1.2053</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6324</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4852</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1472</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9959</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6864</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3095</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1122</v>
+        <v>1.0655</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6487</v>
+        <v>1.4055</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5366</v>
+        <v>-0.34</v>
       </c>
       <c r="G8" t="n">
         <v>0.8806</v>
@@ -1078,13 +1078,13 @@
         <v>0.3964</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1017</v>
+        <v>0.0551</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2423</v>
+        <v>-0.0009</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1406</v>
+        <v>0.0559</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9813</v>
+        <v>1.0219</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2055</v>
+        <v>0.3303</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7759</v>
+        <v>0.6916</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1901</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4123</v>
+        <v>-0.3717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.444</v>
+        <v>-0.3192</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0318</v>
+        <v>-0.0525</v>
       </c>
       <c r="V9" t="n">
         <v>1.4033</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1281</v>
+        <v>0.3434</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3996</v>
+        <v>2.0824</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5277</v>
+        <v>-1.739</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6975</v>
+        <v>3.4638</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0581</v>
+        <v>3.8293</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7556</v>
+        <v>-0.3655</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2765</v>
+        <v>3.369</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4774</v>
+        <v>3.2082</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2009</v>
+        <v>0.1607</v>
       </c>
       <c r="M11" t="n">
-        <v>0.974</v>
+        <v>0.0948</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4193</v>
+        <v>0.621</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5547</v>
+        <v>-0.5262</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3029</v>
+        <v>-0.6378</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.132</v>
+        <v>-0.2954</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1708</v>
+        <v>-0.3424</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2666</v>
+        <v>-2.6808</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2666</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0008</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8787</v>
+        <v>-1.6034</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8794</v>
+        <v>1.6681</v>
       </c>
       <c r="G12" t="n">
-        <v>3.4638</v>
+        <v>0.6975</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8293</v>
+        <v>-0.0581</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3655</v>
+        <v>0.7556</v>
       </c>
       <c r="J12" t="n">
-        <v>3.369</v>
+        <v>-0.2765</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2082</v>
+        <v>-0.4774</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1607</v>
+        <v>0.2009</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0948</v>
+        <v>0.974</v>
       </c>
       <c r="N12" t="n">
-        <v>0.621</v>
+        <v>0.4193</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5262</v>
+        <v>0.5547</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.982</v>
+        <v>-0.3662</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4992</v>
+        <v>-0.3358</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4828</v>
+        <v>-0.0304</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6808</v>
+        <v>-0.2666</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.6808</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2877</v>
+        <v>-4.1805</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0086</v>
+        <v>-1.9857</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2791</v>
+        <v>-2.1948</v>
       </c>
       <c r="G13" t="n">
         <v>-3.8247</v>
@@ -1468,13 +1468,13 @@
         <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2558</v>
+        <v>-0.1487</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3192</v>
+        <v>-0.2963</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0634</v>
+        <v>0.1476</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6036</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.6378</v>
+        <v>-6.0452</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.5421</v>
+        <v>-6.1741</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.1289</v>
       </c>
       <c r="G14" t="n">
         <v>-1.3495</v>
@@ -1546,13 +1546,13 @@
         <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8303</v>
+        <v>-0.2377</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1232</v>
+        <v>-0.7551</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2928</v>
+        <v>0.5174</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8811</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>21.63910000000001</v>
+        <v>22.2631</v>
       </c>
       <c r="E15" t="n">
-        <v>15.11449999999999</v>
+        <v>15.7383</v>
       </c>
       <c r="F15" t="n">
         <v>6.5247</v>
@@ -1600,7 +1600,7 @@
         <v>23.8534</v>
       </c>
       <c r="K15" t="n">
-        <v>8.632400000000001</v>
+        <v>8.632400000000002</v>
       </c>
       <c r="L15" t="n">
         <v>15.2209</v>
@@ -1624,13 +1624,13 @@
         <v>15.8579</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.818000000000001</v>
+        <v>-3.1938</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.2385</v>
+        <v>-3.6145</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4208000000000001</v>
+        <v>0.4205</v>
       </c>
       <c r="V15" t="n">
         <v>3.6211</v>
@@ -1639,7 +1639,7 @@
         <v>9.375300000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-5.754000000000001</v>
+        <v>-5.754</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.421</v>
+        <v>2.0269</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2595</v>
+        <v>2.3427</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1615</v>
+        <v>-0.3158</v>
       </c>
       <c r="G16" t="n">
         <v>0.9583</v>
@@ -1702,13 +1702,13 @@
         <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4569</v>
+        <v>1.0627</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0318</v>
+        <v>0.115</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4251</v>
+        <v>0.9478</v>
       </c>
       <c r="V16" t="n">
         <v>0.6005</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9545</v>
+        <v>1.389</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2477</v>
+        <v>1.7384</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2932</v>
+        <v>-0.3494</v>
       </c>
       <c r="G17" t="n">
         <v>0.9342</v>
@@ -1780,13 +1780,13 @@
         <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9023</v>
+        <v>0.3368</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7967</v>
+        <v>0.2873</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1056</v>
+        <v>0.0495</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8731</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.144</v>
+        <v>0.9935</v>
       </c>
       <c r="E18" t="n">
-        <v>2.12</v>
+        <v>2.3238</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9761</v>
+        <v>-1.3303</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7059</v>
@@ -1858,13 +1858,13 @@
         <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7329</v>
+        <v>0.1166</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8184</v>
+        <v>-0.6147</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.7313</v>
       </c>
       <c r="V18" t="n">
         <v>-0.003</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0767</v>
+        <v>-1.0061</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1235</v>
+        <v>-1.716</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0468</v>
+        <v>0.7099</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1058</v>
@@ -1936,13 +1936,13 @@
         <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4507</v>
+        <v>0.5212</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8112</v>
+        <v>-0.4037</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2619</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0.5784</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0437</v>
+        <v>-2.6434</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6676</v>
+        <v>-2.4639</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3761</v>
+        <v>-0.1795</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3254</v>
@@ -2014,13 +2014,13 @@
         <v>2.3787</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0504</v>
+        <v>0.4507</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1103</v>
+        <v>0.3141</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0599</v>
+        <v>0.1366</v>
       </c>
       <c r="V20" t="n">
         <v>-0.174</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3949</v>
+        <v>-3.3002</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5511</v>
+        <v>-1.653</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8438</v>
+        <v>-1.6473</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9394</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>0.322</v>
+        <v>0.4167</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0479</v>
+        <v>-0.054</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2741</v>
+        <v>0.4707</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7776</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6435</v>
+        <v>-3.7101</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0877</v>
+        <v>-0.9858</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5558</v>
+        <v>-2.7243</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9003</v>
@@ -2170,13 +2170,13 @@
         <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3355</v>
+        <v>0.2689</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0072</v>
+        <v>0.0946</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3427</v>
+        <v>0.1743</v>
       </c>
       <c r="V22" t="n">
         <v>0.3088</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ CAMPOS</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4406</v>
+        <v>-4.0848</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1346</v>
+        <v>-3.1833</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3059</v>
+        <v>-0.9014</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5732</v>
+        <v>-5.3087</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3539</v>
+        <v>-2.3337</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2194</v>
+        <v>-2.975</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7572</v>
+        <v>-3.1137</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7131</v>
+        <v>-1.1968</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0441</v>
+        <v>-1.9169</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3304</v>
+        <v>-2.195</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.067</v>
+        <v>-1.1369</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2634</v>
+        <v>-1.0581</v>
       </c>
       <c r="P23" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-0.1982</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-1.1893</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6777</v>
+        <v>0.2249</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2975</v>
+        <v>0.1286</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3802</v>
+        <v>0.0963</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.3468</v>
+        <v>0.4044</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3468</v>
+        <v>0.4044</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>H. FERNANDEZ CAMPOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8716</v>
+        <v>-4.7566</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9983</v>
+        <v>-0.3384</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8733</v>
+        <v>-4.4183</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.3087</v>
+        <v>-2.5732</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3337</v>
+        <v>-0.3539</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.975</v>
+        <v>-2.2194</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1137</v>
+        <v>0.7572</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1968</v>
+        <v>0.7131</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9169</v>
+        <v>0.0441</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.195</v>
+        <v>-3.3304</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1369</v>
+        <v>-1.067</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0581</v>
+        <v>-2.2634</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5947</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.3616</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6864</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1243</v>
+        <v>0.2679</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4044</v>
+        <v>-2.3468</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.4044</v>
+        <v>-2.3468</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6876</v>
+        <v>-6.5472</v>
       </c>
       <c r="E25" t="n">
         <v>-2.5891</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.0985</v>
+        <v>-3.9581</v>
       </c>
       <c r="G25" t="n">
         <v>-2.8874</v>
@@ -2404,13 +2404,13 @@
         <v>0.7929</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="T25" t="n">
         <v>-0.3816</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2991</v>
+        <v>0.4395</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3389</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.6391</v>
+        <v>-21.639</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.524699999999999</v>
+        <v>-6.524600000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-15.1144</v>
+        <v>-15.1145</v>
       </c>
       <c r="G26" t="n">
         <v>-19.8536</v>
@@ -2467,7 +2467,7 @@
         <v>-23.8536</v>
       </c>
       <c r="N26" t="n">
-        <v>-8.6326</v>
+        <v>-8.632599999999998</v>
       </c>
       <c r="O26" t="n">
         <v>-15.221</v>
@@ -2482,13 +2482,13 @@
         <v>13.8756</v>
       </c>
       <c r="S26" t="n">
-        <v>3.818</v>
+        <v>3.8179</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4205999999999999</v>
+        <v>-0.4206</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2386</v>
+        <v>4.2388</v>
       </c>
       <c r="V26" t="n">
         <v>-3.6213</v>
@@ -2497,7 +2497,7 @@
         <v>5.753900000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.375300000000001</v>
+        <v>-9.375299999999999</v>
       </c>
     </row>
   </sheetData>
